--- a/docs/data-collection/信用卡優惠資料整理模板-v4-2026-08-21.xlsx
+++ b/docs/data-collection/信用卡優惠資料整理模板-v4-2026-08-21.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1043,10 +1043,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1059,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.25" customWidth="1" min="1" max="1"/>
@@ -1344,6 +1340,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1356,7 +1353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.8799991607666" customWidth="1" min="1" max="1"/>
@@ -2825,6 +2822,137 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>星展PChome Prime聯名卡</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>dbs-pchome-prime-card</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>dbs</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.dbs.com.tw/personal-zh/cards/dbs-pchomeprime/index.html</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PChome 24h購物與書店最高6%回饋，週四購物另有加碼。</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>星展PChome Prime聯名卡適合以PChome 24h購物與PChome 24h書店為主要網購通路者。2026年底前，正卡綁定PChome帳號後可累積站內PChome聯名點數與P幣；每週四以指定方式全額付款可再享P幣加碼。另有指定海外電商加碼活動，均依官方條件與回饋上限認定。</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>經常在PChome 24h購物或PChome 24h書店消費，願意綁定PChome帳號並配合週四購物的使用者。</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>正卡 NT$2,400；附卡免年費</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>首年免年費；次年起符合年度消費任一筆、年度消費滿NT$30,000，或全年使用電子帳單等任一條件，可免次年年費。</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>PChome 24h購物與書店一般消費最高6%回饋
+每週四指定方式全額付款可再加碼2% P幣
+指定海外電商另有加碼活動</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>PChome商店街與露天拍賣不適用站內回饋
+購買PChome儲值金或以儲值金付款，不享P幣與週四加碼
+回饋上限、付款方式與指定商店均以星展公告為準</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>官方資料查證：2026-08-21；卡片等級與發卡組織未在本次官方來源中逐卡別確認，暫留空白。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>國泰蝦皮購物聯名卡</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>cathay-shopee-shopping-card</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>cathay</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.cathaybk.com.tw/cathaybk/personal/credit-card/cards/choose-card-s1/?a=1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>蝦皮全站消費依月累積金額最高4%蝦幣，另有免運券門檻優惠。</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>國泰蝦皮購物聯名卡以蝦皮全站直接結帳回饋為核心。2026年底前，依每月帳單累積的蝦皮全站消費金額，未滿NT$3,000最高3%蝦幣，滿NT$3,000最高4%蝦幣；達一般消費指定門檻或筆數，另可獲蝦皮免運券。</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>經常直接在蝦皮購物結帳，且每月蝦皮消費可累積至NT$3,000以上的使用者。</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>正卡 NT$1,800；附卡免年費</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>申辦電子帳單且年消費滿1次，或年消費滿6次，或年消費滿NT$30,000，可免次年年費。</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>蝦皮全站月累積消費滿NT$3,000最高4%蝦幣
+月月達一般消費門檻或筆數，可獲免運券</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>LINE Pay、街口支付、蝦皮廣告、海外消費與蝦皮跨境交易不適用蝦皮全站回饋
+國泰加碼蝦幣有每卡年度上限
+蝦皮平台回饋與免運券依蝦皮規則發放及使用</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>官方資料查證：2026-08-21；卡片等級與發卡組織未在本次官方來源中逐卡別確認，暫留空白。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2837,7 +2965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:T54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.75" customWidth="1" min="1" max="1"/>
@@ -3860,18 +3988,22 @@
       </c>
       <c r="L11" s="18" t="inlineStr">
         <is>
-          <t>3.8%</t>
-        </is>
-      </c>
-      <c r="M11" s="18" t="n"/>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="inlineStr">
+        <is>
+          <t>各方案每期帳單適用加碼之消費金額，以持卡人永久信用額度加計 NT$300,000 為限；超出部分僅適用一般消費 0.3%。</t>
+        </is>
+      </c>
       <c r="N11" s="18" t="inlineStr">
         <is>
-          <t>完成台新帳戶自動扣繳台新信用卡帳款，並在消費前於 Richart Life APP 切換適用方案</t>
+          <t>持有台新 Richart 卡，於 Richart Life App 切換任一方案即可，不需額外設定。</t>
         </is>
       </c>
       <c r="O11" s="18" t="inlineStr">
         <is>
-          <t>自扣須在帳單結帳日 3 個工作天前成功設定且持續未取消；升級資格於次期帳單結帳後次營業日生效。方案按正卡人歸戶，每日僅能擇一方案、每日限切換一次。指定通路、支付方式與不回饋項目依台新公告認定；正附卡交易逐筆計算，回饋於入帳日後次二營業日入帳。</t>
+          <t>每位正卡人每日限轉換一次，方案依正卡人設定計算，正附卡交易於入帳日後次二營業日統一回饋至正卡人帳戶。指定通路、支付方式與不回饋項目依台新公告認定。</t>
         </is>
       </c>
       <c r="P11" s="18" t="inlineStr">
@@ -3894,2403 +4026,3405 @@
           <t>官方卡片頁查證；本列為主權益，個別方案之通路、回饋上限與支付限制請依台新當期公告。</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>LEVEL 1（核卡即享）</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="66" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="18" t="n"/>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>taishin-richart-switch-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>指定火鍋燒肉品牌 10%；日常續命飲品 10%；約會犒賞餐廳 5%；追星應援平台 5%；熬夜追更娛樂 5%；數位外掛服務 3.3%</t>
+        </is>
+      </c>
+      <c r="M12" s="18" t="inlineStr">
+        <is>
+          <t>各方案每期帳單適用加碼之消費金額，以持卡人永久信用額度加計 NT$300,000 為限；超出部分僅適用一般消費 0.3%。</t>
+        </is>
+      </c>
+      <c r="N12" s="18" t="inlineStr">
+        <is>
+          <t>完成台新帳戶自動扣繳信用卡款並升級 LEVEL 2，消費前於 App 切換 Chill刷；2026/7/8–9/30 適用。</t>
+        </is>
+      </c>
+      <c r="O12" s="18" t="inlineStr">
+        <is>
+          <t>指定餐廳例：詹記麻辣火鍋、萬客什鍋、海底撈、雞湯大叔、屋馬燒肉、茶六燒肉堂、新村站著吃、燒肉政宗、碳佐麻里。付款限實體卡（含輸入卡號）、台新Pay、Apple Pay、Google錢包、Samsung Pay、LINE Pay；街口支付、台灣Pay、My FamiPay、全支付、OPEN錢包、中油Pay等不適用。</t>
+        </is>
+      </c>
+      <c r="P12" s="18" t="n"/>
+      <c r="Q12" s="18" t="n"/>
+      <c r="R12" s="18" t="n"/>
+      <c r="S12" s="18" t="n"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Chill刷（火鍋燒肉／飲品／娛樂）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52.79999923706055" customHeight="1">
+      <c r="A13" s="18" t="n"/>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>taishin-richart-switch-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="n"/>
+      <c r="I13" s="18" t="n"/>
+      <c r="J13" s="18" t="n"/>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>台新Pay及台新Pay+ 3.8%；LINE Pay及全盈+Pay 2.3%</t>
+        </is>
+      </c>
+      <c r="M13" s="18" t="inlineStr">
+        <is>
+          <t>各方案每期帳單適用加碼之消費金額，以持卡人永久信用額度加計 NT$300,000 為限；超出部分僅適用一般消費 0.3%。</t>
+        </is>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
+        <is>
+          <t>完成台新帳戶自動扣繳信用卡款並升級 LEVEL 2，消費前於 App 切換 Pay著刷。</t>
+        </is>
+      </c>
+      <c r="O13" s="18" t="inlineStr">
+        <is>
+          <t>每位正卡人每日限轉換一次，方案依正卡人設定計算，正附卡交易於入帳日後次二營業日統一回饋至正卡人帳戶。指定通路、支付方式與不回饋項目依台新公告認定。</t>
+        </is>
+      </c>
+      <c r="P13" s="18" t="n"/>
+      <c r="Q13" s="18" t="n"/>
+      <c r="R13" s="18" t="n"/>
+      <c r="S13" s="18" t="n"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Pay著刷（行動支付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1">
+      <c r="A14" s="18" t="n"/>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>taishin-richart-switch-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="18" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L14" s="18" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="M14" s="18" t="inlineStr">
+        <is>
+          <t>各方案每期帳單適用加碼之消費金額，以持卡人永久信用額度加計 NT$300,000 為限；超出部分僅適用一般消費 0.3%。</t>
+        </is>
+      </c>
+      <c r="N14" s="18" t="inlineStr">
+        <is>
+          <t>完成台新帳戶自動扣繳信用卡款並升級 LEVEL 2，消費前於 App 切換天天刷。</t>
+        </is>
+      </c>
+      <c r="O14" s="18" t="inlineStr">
+        <is>
+          <t>指定通路例：全家、7-11、萬家福、樂家康、大買家；臺鐵、高鐵、台灣大車隊、LINEGO、Yoxi、Uber、台灣Bolt；中油直營、全國加油、充電站；寶雅、康是美、屈臣氏等藥妝藥局。</t>
+        </is>
+      </c>
+      <c r="P14" s="18" t="n"/>
+      <c r="Q14" s="18" t="n"/>
+      <c r="R14" s="18" t="n"/>
+      <c r="S14" s="18" t="n"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>天天刷（超商／交通／加油／藥妝）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="n"/>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>taishin-richart-switch-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="M15" s="18" t="inlineStr">
+        <is>
+          <t>各方案每期帳單適用加碼之消費金額，以持卡人永久信用額度加計 NT$300,000 為限；超出部分僅適用一般消費 0.3%。</t>
+        </is>
+      </c>
+      <c r="N15" s="18" t="inlineStr">
+        <is>
+          <t>完成台新帳戶自動扣繳信用卡款並升級 LEVEL 2，消費前於 App 切換大筆刷。</t>
+        </is>
+      </c>
+      <c r="O15" s="18" t="inlineStr">
+        <is>
+          <t>指定通路例：新光三越、遠東百貨、遠東SOGO等指定百貨；MITSUI OUTLET PARK、華泰名品城等 Outlet；IKEA、特力屋等居家裝修；UNIQLO、ZARA 等時尚品牌。</t>
+        </is>
+      </c>
+      <c r="P15" s="18" t="n"/>
+      <c r="Q15" s="18" t="n"/>
+      <c r="R15" s="18" t="n"/>
+      <c r="S15" s="18" t="n"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>大筆刷（百貨／Outlet／居家／服飾）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="n"/>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>taishin-richart-switch-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="M16" s="18" t="inlineStr">
+        <is>
+          <t>各方案每期帳單適用加碼之消費金額，以持卡人永久信用額度加計 NT$300,000 為限；超出部分僅適用一般消費 0.3%。</t>
+        </is>
+      </c>
+      <c r="N16" s="18" t="inlineStr">
+        <is>
+          <t>完成台新帳戶自動扣繳信用卡款並升級 LEVEL 2，消費前於 App 切換好饗刷；不適用 LINE Pay。</t>
+        </is>
+      </c>
+      <c r="O16" s="18" t="inlineStr">
+        <is>
+          <t>涵蓋全臺餐飲（不含餐券）、Uber Eats／Foodpanda 外送、拓元／KKTIX 等購票娛樂、錢櫃／好樂迪等指定 KTV、晶華／雲朗等指定飯店。　外送（Uber Eats、Foodpanda）僅適用好饗刷 3.3%，Pay著刷 3.8% 不適用外送平台消費，且每日僅能擇一方案。</t>
+        </is>
+      </c>
+      <c r="P16" s="18" t="n"/>
+      <c r="Q16" s="18" t="n"/>
+      <c r="R16" s="18" t="n"/>
+      <c r="S16" s="18" t="n"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>好饗刷（全台餐飲／外送／購票／飯店）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="n"/>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>taishin-richart-switch-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="n"/>
+      <c r="I17" s="18" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="18" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L17" s="18" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="M17" s="18" t="inlineStr">
+        <is>
+          <t>各方案每期帳單適用加碼之消費金額，以持卡人永久信用額度加計 NT$300,000 為限；超出部分僅適用一般消費 0.3%。</t>
+        </is>
+      </c>
+      <c r="N17" s="18" t="inlineStr">
+        <is>
+          <t>完成台新帳戶自動扣繳信用卡款並升級 LEVEL 2，消費前於 App 切換數趣刷。</t>
+        </is>
+      </c>
+      <c r="O17" s="18" t="inlineStr">
+        <is>
+          <t>指定通路例：蝦皮、momo、PChome 等網購；知識衛星、Hahow 等線上課程；Netflix、Disney+ 等影音；ChatGPT、Canva 等 AI 服務。</t>
+        </is>
+      </c>
+      <c r="P17" s="18" t="n"/>
+      <c r="Q17" s="18" t="n"/>
+      <c r="R17" s="18" t="n"/>
+      <c r="S17" s="18" t="n"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>數趣刷（網購／線上課程／影音／AI服務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="n"/>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>taishin-richart-switch-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="n"/>
+      <c r="I18" s="18" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="18" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L18" s="18" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="M18" s="18" t="inlineStr">
+        <is>
+          <t>各方案每期帳單適用加碼之消費金額，以持卡人永久信用額度加計 NT$300,000 為限；超出部分僅適用一般消費 0.3%。</t>
+        </is>
+      </c>
+      <c r="N18" s="18" t="inlineStr">
+        <is>
+          <t>完成台新帳戶自動扣繳信用卡款並升級 LEVEL 2，消費前於 App 切換玩旅刷。</t>
+        </is>
+      </c>
+      <c r="O18" s="18" t="inlineStr">
+        <is>
+          <t>涵蓋海外消費（含實體及線上）、中華航空／長榮等航空公司、Klook／Agoda 等訂房平台、雄獅／易遊網等旅行社。</t>
+        </is>
+      </c>
+      <c r="P18" s="18" t="n"/>
+      <c r="Q18" s="18" t="n"/>
+      <c r="R18" s="18" t="n"/>
+      <c r="S18" s="18" t="n"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>玩旅刷（海外消費／航空／訂房／旅行社）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="n"/>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>taishin-richart-switch-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="n"/>
+      <c r="I19" s="18" t="n"/>
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="18" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L19" s="18" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="M19" s="18" t="inlineStr">
+        <is>
+          <t>各方案每期帳單適用加碼之消費金額，以持卡人永久信用額度加計 NT$300,000 為限；超出部分僅適用一般消費 0.3%。</t>
+        </is>
+      </c>
+      <c r="N19" s="18" t="inlineStr">
+        <is>
+          <t>完成台新帳戶自動扣繳信用卡款並升級 LEVEL 2，消費前於 App 切換假日刷。</t>
+        </is>
+      </c>
+      <c r="O19" s="18" t="inlineStr">
+        <is>
+          <t>國內節假日不限通路皆適用。</t>
+        </is>
+      </c>
+      <c r="P19" s="18" t="n"/>
+      <c r="Q19" s="18" t="n"/>
+      <c r="R19" s="18" t="n"/>
+      <c r="S19" s="18" t="n"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>假日刷（國內節假日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="n"/>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>taishin-richart-switch-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="18" t="n"/>
+      <c r="I20" s="18" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L20" s="18" t="inlineStr">
+        <is>
+          <t>一般消費 0.3%（無上限）；保費一次付清 1.3%</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="n"/>
+      <c r="N20" s="18" t="inlineStr">
+        <is>
+          <t>不需切換方案，一般消費自動適用；保費一次付清另計。</t>
+        </is>
+      </c>
+      <c r="O20" s="18" t="inlineStr">
+        <is>
+          <t>超出各方案加碼上限（NT$300,000）之消費，僅回饋一般消費 0.3%。</t>
+        </is>
+      </c>
+      <c r="P20" s="18" t="n"/>
+      <c r="Q20" s="18" t="n"/>
+      <c r="R20" s="18" t="n"/>
+      <c r="S20" s="18" t="n"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>一般消費／保費</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>永豐信用卡指定稅款滿 NT$3,000 分 6 期 0 利率</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>sinopac-designated-tax-installment-2026h1</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>installment</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>2026-07-01 至 12-31 以 Paytax 或大咖 DACARD 繳牌照稅、房屋稅、地價稅，單筆滿 NT$3,000 登錄享 6 期 0 利率</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>繳納牌照稅、房屋稅或地價稅，且有分期資金需求的永豐信用卡正卡持卡人。</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F21" s="18" t="inlineStr">
         <is>
           <t>指定稅款單筆滿 NT$3,000，分 6 期 0 利率</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G21" s="18" t="inlineStr">
         <is>
           <t>Paytax／大咖 DACARD 繳納，免手續費</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="H21" s="18" t="inlineStr">
         <is>
           <t>2026-07-01 至 12-31，持永豐信用卡透過 Paytax 繳稅服務網（網路、QR Code 或中華電信語音）或大咖 DACARD APP 繳納牌照稅、房屋稅、地價稅；正卡持卡人完成分期總約簽署並於登錄當月繳納單筆滿 NT$3,000，登錄後可享 6 期 0 利率。指定稅款同時提供免手續費；活動另有符合歷史代繳條件者的 0.2% 刷卡金方案。</t>
         </is>
       </c>
-      <c r="I12" s="18" t="inlineStr">
+      <c r="I21" s="18" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J12" s="18" t="inlineStr">
+      <c r="J21" s="18" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="K12" s="18" t="inlineStr">
+      <c r="K21" s="18" t="inlineStr">
         <is>
           <t>分期</t>
         </is>
       </c>
-      <c r="L12" s="18" t="inlineStr">
+      <c r="L21" s="18" t="inlineStr">
         <is>
           <t>6期0利率</t>
         </is>
       </c>
-      <c r="M12" s="18" t="n"/>
-      <c r="N12" s="18" t="inlineStr">
+      <c r="M21" s="18" t="n"/>
+      <c r="N21" s="18" t="inlineStr">
         <is>
           <t>單筆指定稅款滿 NT$3,000，並於登錄當月繳納</t>
         </is>
       </c>
-      <c r="O12" s="18" t="inlineStr">
+      <c r="O21" s="18" t="inlineStr">
         <is>
           <t>限牌照稅、房屋稅、地價稅；限正卡持卡人於 Paytax（網路、QR Code、中華電信語音）或大咖 DACARD APP 繳納，不含便利商店代收、公務機關臨櫃及第三方支付。須於繳納當月底前簽署消費分期總約並完成活動登錄；分期金額占用永久額度。稅款不列入一般消費，八通卡、公司卡、配銷卡、儲值卡及簽帳金融卡不適用。</t>
         </is>
       </c>
-      <c r="P12" s="18" t="inlineStr">
+      <c r="P21" s="18" t="inlineStr">
         <is>
           <t>https://bank.sinopac.com/sinopacbt/personal/credit-card/discount/650410355.html</t>
         </is>
       </c>
-      <c r="Q12" s="18" t="inlineStr">
+      <c r="Q21" s="18" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="R12" s="18" t="inlineStr">
+      <c r="R21" s="18" t="inlineStr">
         <is>
           <t>繳稅,分期,需登錄,期間限定</t>
         </is>
       </c>
-      <c r="S12" s="18" t="inlineStr">
+      <c r="S21" s="18" t="inlineStr">
         <is>
           <t>官方活動頁查證。活動已於 2026-06-30 結束，保留為 2026 報稅季可查核資料；後續年度需重新查證。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="52.79999923706055" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>永豐信用卡繳學費滿額最高回饋 NT$500</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>sinopac-tuition-payment-rebate-2026h1</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>2026-07-01 至 12-31 透過 i 繳費或學費通繳學費並登錄，當月每滿 NT$50,000 回饋 NT$50，最高 NT$500</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>有大額學費支出，並可在繳費當月完成活動登錄的永豐信用卡正卡持卡人。</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>當月每滿 NT$50,000 回饋 NT$50 刷卡金</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="G22" s="18" t="inlineStr">
         <is>
           <t>每戶每月最高回饋 NT$500 刷卡金</t>
         </is>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H22" s="18" t="inlineStr">
         <is>
           <t>2026-07-01 至 12-31，透過 i 繳費或聯合信用卡中心學費通平台使用永豐信用卡繳納學費，於繳費當月完成活動登錄後，正附卡合併的當月學費每滿 NT$50,000 回饋 NT$50 刷卡金，每戶每月最高 NT$500；回饋於代繳成功次次月起入帳。另可依單筆分期活動申請 0 利率分期。</t>
         </is>
       </c>
-      <c r="I13" s="18" t="inlineStr">
+      <c r="I22" s="18" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="J22" s="18" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="K13" s="18" t="inlineStr">
+      <c r="K22" s="18" t="inlineStr">
         <is>
           <t>現金回饋</t>
         </is>
       </c>
-      <c r="L13" s="18" t="inlineStr">
+      <c r="L22" s="18" t="inlineStr">
         <is>
           <t>每滿NT$50,000回饋NT$50</t>
         </is>
       </c>
-      <c r="M13" s="18" t="inlineStr">
+      <c r="M22" s="18" t="inlineStr">
         <is>
           <t>每戶每月最高NT$500</t>
         </is>
       </c>
-      <c r="N13" s="18" t="inlineStr">
+      <c r="N22" s="18" t="inlineStr">
         <is>
           <t>繳費當月透過 i 繳費或學費通繳納學費並完成活動登錄</t>
         </is>
       </c>
-      <c r="O13" s="18" t="inlineStr">
+      <c r="O22" s="18" t="inlineStr">
         <is>
           <t>僅限 i 繳費、聯合信用卡中心學費通平台，其他繳費方式不適用；須在繳費當月完成登錄，逾期不可補登。公司卡、配銷卡、八通卡、儲值卡及簽帳金融卡不適用；學費不列入一般消費。</t>
         </is>
       </c>
-      <c r="P13" s="18" t="inlineStr">
+      <c r="P22" s="18" t="inlineStr">
         <is>
           <t>https://bank.sinopac.com/sinopacbt/personal/credit-card/discount/650410355.html</t>
         </is>
       </c>
-      <c r="Q13" s="18" t="inlineStr">
+      <c r="Q22" s="18" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="R13" s="18" t="inlineStr">
+      <c r="R22" s="18" t="inlineStr">
         <is>
           <t>學費,需登錄,期間限定</t>
         </is>
       </c>
-      <c r="S13" s="18" t="inlineStr">
+      <c r="S22" s="18" t="inlineStr">
         <is>
           <t>官方活動頁查證。活動已於 2026-06-30 結束，保留為 2026 上半年學費季可查核資料；後續學期需重新查證。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="66" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>永豐信用卡公共事業費自動代扣繳最高 2% 回饋</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>sinopac-utilities-autopay-2percent-2026h2</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>2026-08-01 至 10-31 先完成兩項水電瓦斯／電信自扣任務並登錄，代扣繳公共事業費享 2% 回饋，最高 NT$50</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>可在 2026-07-31 前完成兩項公共事業費自動代扣繳，並願意在 8 月登錄的永豐信用卡正卡持卡人。</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>水費、電費、瓦斯費、中華電信費等自扣繳可適用</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="G23" s="18" t="inlineStr">
         <is>
           <t>完成任務後代扣繳享 2%，最高 NT$50</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="H23" s="18" t="inlineStr">
         <is>
           <t>2026-08-01 至 10-31，持永豐信用卡以線上申請、DACARD 大咖 APP、公用事業費代繳約定書或信用卡申請書，申請水費、電費、瓦斯費、公有路邊停車費或中華電信費自動代扣繳。若在 2026-01-01 至 07-31 期間申請任二項且完成自動代扣繳總次數達 4 次，並於 8 月成功登錄，可在活動期間享 2% 刷卡金回饋，最高 NT$50。</t>
         </is>
       </c>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="I23" s="18" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="J23" s="18" t="inlineStr">
         <is>
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="K14" s="18" t="inlineStr">
+      <c r="K23" s="18" t="inlineStr">
         <is>
           <t>現金回饋</t>
         </is>
       </c>
-      <c r="L14" s="18" t="inlineStr">
+      <c r="L23" s="18" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="M14" s="18" t="inlineStr">
+      <c r="M23" s="18" t="inlineStr">
         <is>
           <t>最高NT$50</t>
         </is>
       </c>
-      <c r="N14" s="18" t="inlineStr">
+      <c r="N23" s="18" t="inlineStr">
         <is>
           <t>2026-07-31 前申請公共事業費任二項，完成自扣總次數達4次，並於8月完成登錄</t>
         </is>
       </c>
-      <c r="O14" s="18" t="inlineStr">
+      <c r="O23" s="18" t="inlineStr">
         <is>
           <t>限指定申請方式的自動代扣繳，單次透過財金繳費稅平台、全國繳費網或其他繳費平台不適用。限量 5,000 名，8 月 1 日開放登錄；八通卡、公司卡、配銷卡及簽帳金融卡不適用。水電瓦斯及電信費不屬一般消費。</t>
         </is>
       </c>
-      <c r="P14" s="18" t="inlineStr">
+      <c r="P23" s="18" t="inlineStr">
         <is>
           <t>https://bank.sinopac.com/sinopacbt/personal/credit-card/discount/650410355.html</t>
         </is>
       </c>
-      <c r="Q14" s="18" t="inlineStr">
+      <c r="Q23" s="18" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="R14" s="18" t="inlineStr">
+      <c r="R23" s="18" t="inlineStr">
         <is>
           <t>水電瓦斯,電信費,加碼,需登錄,期間限定</t>
         </is>
       </c>
-      <c r="S14" s="18" t="inlineStr">
+      <c r="S23" s="18" t="inlineStr">
         <is>
           <t>官方活動頁查證；活動尚未開始。首扣優惠（2026-01-01 至 12-31）亦在同頁，惟本列聚焦可量化的 2% 夏日加碼。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>聯邦綠卡指定生活代扣繳每月1%刷卡金</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ubot-green-card-utilities-autopay-2026h2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>cashback</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-07-01至12-31完成登錄，以聯邦綠卡綁水電瓦斯或電信費自動代扣繳並申辦電子化帳單，每月享1%刷卡金、上限NT$100</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>有固定水電、瓦斯或電信費帳單，想使用信用卡自動代扣繳並可申辦電子化帳單者。</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>完成活動登錄，並以聯邦綠卡綁定指定生活代扣繳與電子化帳單</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>指定生活代扣繳每月1%刷卡金</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-07-01至12-31，聯邦綠卡持卡人完成活動登錄後，綁定台灣自來水、台北自來水、台電、中華電信、台灣大哥大、遠傳電信、指定瓦斯公司或指定公有路邊停車費等生活代扣繳；申辦電子化帳單，即享每月1%刷卡金，月上限NT$100。</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>現金回饋</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>每月最高NT$100</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>活動期間完成登錄，以聯邦綠卡綁定指定生活代扣繳並申辦電子化帳單</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>生活代扣繳非一般消費，不提供原始卡片回饋；須以聯邦認定交易名稱為準。Visa金融卡、商務差旅卡、採購卡不適用；指定業者與完整條款以官方活動頁為準。</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>https://activity.ubot.com.tw/aws_act/2026/202607autopay/index.htm</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>水電瓦斯,電信費,加碼,需登錄,期間限定</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>官方活動頁查證；僅收錄聯邦綠卡專屬每月1%回饋，不將新申辦首扣贈刷卡金混列。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>台新信用卡繳國內學雜費分期最優3.88%起</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>taishin-tuition-installment-2026h2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>installment</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-07-10至12-31，刷台新信用卡繳國內學雜費單筆滿NT$1,000，分3／6期利率3.88%起且0手續費</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>需繳國內學雜費並希望以信用卡分期付款的台新信用卡持卡人。</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>單筆學雜費滿NT$1,000</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>分3／6期3.88%、12期5.88%、18／24／30期8.88%，均0手續費</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-07-10至12-31，刷台新信用卡繳納幼稚園、國小、國高中、大專院校、進修推廣、國內美國學校及外僑學校等國內學雜費；單筆滿NT$1,000可享分3／6期3.88%、12期5.88%、18／24／30期8.88%優惠利率，均0手續費。</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>分期</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>3／6期3.88%起、0手續費</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>繳納前至官網登錄；數位通路免登錄。街口支付或悠遊付繳費後，須進線台新客服辦理分期</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>便利商店繳學雜費不適用。活動期間僅須登錄一次，後續每筆可享自動分期；如已設定指定卡片分期，欲參加本活動須進線台新客服。可繳學校與繳費帳號依繳款單及繳費平台公告為準。</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>https://mkpcard.taishinbank.com.tw/tscccms/promotion/detail/WM_20260617134739441</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>學費,分期,需登錄,期間限定</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>官方活動頁查證；全體適用台新信用卡，先連結既有台新Richart卡。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>台新街口聯名卡綁街口APP繳稅費最高2.15%</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>taishin-jkopay-card-bill-payments-2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>cashback</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026全年綁街口聯名卡於街口APP繳稅費，基本0.15%無上限；當月繳費滿NT$1,000再享2%街口券、每月上限20元</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>使用街口支付APP繳稅費或學雜費，且可每月累積NT$1,000繳費並手動領券的街口聯名卡持卡人。</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>當月街口APP繳費交易滿NT$1,000可取得加碼</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>基本0.15%街口幣無上限，加碼2%街口券</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-01-01至12-31，街口聯名卡綁定街口支付APP繳稅費可享基本0.15%回饋無上限；當月街口APP繳費交易滿NT$1,000，手動領券後可再享2%街口券，每月每人上限20元。官方頁另明載可用街口支付繳學雜費，實際可繳學校依街口支付公告為準。</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>點數回饋</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>最高2.15%</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>加碼2%每月每人上限20元街口券；2026-07-01起每月限量55,000名</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>交易與回饋當下均在街口支付APP綁定街口聯名卡；達NT$1,000後至APP手動領取加碼券</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>領券以系統領取時間判定，額滿無法補領；加碼為街口券，可於全台7-ELEVEN折抵，非現金。若取消綁定本卡或註銷街口支付帳號，視同放棄回饋；繳納項目與學校依街口支付公告。</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>https://www.taishinbank.com.tw/TSB/personal/credit/intro/overview/future/24e1ad87-2cad-11f1-b50f-0050568c09e3</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>繳稅,學費,水電瓦斯,行動支付,加碼,需登錄,期間限定</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>官方活動頁與台新學雜費活動頁交叉查證；水／電等費用與學雜費均有台新官方頁明載。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>中國信託LINE Pay卡回饋計畫最高16%</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ctbc-linepay-rewards-2026h2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>cashback</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026下半年刷中國信託LINE Pay卡，國內外一般消費1%、國外實體信用卡最高2.8%，指定商家加碼最高16%。</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>想把日常、海外與指定商家消費累積為 LINE POINTS 的 LINE Pay 使用者。</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>國內外一般消費1%</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>指定商家加碼最高16%</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>活動期間 2026/7/1-2026/12/31。使用中國信託LINE Pay卡或以 LINE Pay 綁定該卡支付，並於刷卡前完成 LINE Pay 帳號綁定，可累積 LINE POINTS。國內外一般消費享1%；信用卡於國外實體商店面對面交易最高2.8%；指定餐飲、網購、旅遊、生活等合作商家依各活動頁公告加碼，最高16%。</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-12-29</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>點數回饋</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>無上限；點數依消費金額四捨五入入點。</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>以中國信託LINE Pay卡結帳，或 LINE Pay 綁定中國信託LINE Pay卡支付。</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>需於刷卡消費前完成 LINE Pay 帳號綁定。分期交易不回饋 LINE POINTS；信用卡年費、利息、預借現金、基金、學費、稅款、公用事業費、政府規費、便利商店、全聯/大全聯、電信費、部分歐洲地區實體商店等官方列示項目不列入回饋。</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/index.html</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>中信,中國信託,LINE Pay,LINE POINTS,海外消費,一般消費,指定商家</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>補齊：正式站既有資料（多層回饋，3層），本次依 v7 多層寫法重新寫回 xlsx 存檔，未變更資料庫內容。</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>國內外一般消費</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ctbc-linepay-rewards-2026h2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>點數回饋</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>最高2.8%</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>無上限；含一般消費1%與國外實體商店加碼1.8%。</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>限信用卡於國外實體商店面對面交易，含實體卡與 Apple Pay／Google Pay／Samsung Pay。</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>網路交易、條碼支付、第三方支付不列入國外實體商店加碼；是否符合以中國信託及國際組織系統資料為準。需於刷卡消費前完成 LINE Pay 帳號綁定。分期交易不回饋 LINE POINTS；其餘不回饋項目同上。</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>國外實體商店</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ctbc-linepay-rewards-2026h2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>點數回饋</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>最高16%</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>各商家活動期間、登錄名額與回饋上限不同，依官網各活動頁為準。</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>需符合指定商家、指定卡別、指定消費日、滿額或登錄等條件。</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>部分商店位於百貨、商場、機場、車站、飯店或旅館時，可能因帳單明細不同而無法認列加碼。</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>指定商家加碼</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>中國信託LINE Pay卡海外實體消費周周登最高5%</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ctbc-linepay-overseas-physical-weekly-2026q3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>travel</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026/7/1-9/30 持中國信託LINE Pay信用卡至國外實體商店消費，登錄後最高享 LINE POINTS 5%。</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026第三季有海外實體商店消費，且願意每週二搶登錄名額的 LINE Pay卡信用卡持卡人。</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>海外實體最高5%</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>每週二3,000名登錄名額</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>活動期間 2026/7/1-2026/9/30。持中國信託LINE Pay信用卡至國外實體商店消費，活動登錄後享 LINE POINTS 最高5%，包含國外實體一般消費2.8%與2.2%加碼回饋。每週二開放3,000名登錄名額。</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>點數回饋</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>最高5%</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>每週二開放3,000名登錄名額；實際仍以中國信託活動登錄頁公告為準。</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>須持中國信託LINE Pay信用卡於國外實體商店消費並完成活動登錄。</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>LINE Pay簽帳金融卡不適用此活動。國外實體交易認定與不回饋項目依中國信託官網與活動登錄頁公告為準。</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/index.html</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>中信,LINE Pay,海外,實體商店,周周登,LINE POINTS</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>海外實體周周登</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>中國信託LINE Pay卡新戶首刷禮最高300點</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ctbc-linepay-new-card-gift-2026h2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>cashback</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026/7/1-12/31 申辦 LINE Pay 卡，核卡日起30日內累積消費滿NT$888，新戶享300點、新卡享100點 LINE POINTS。</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>首次申辦中國信託信用卡或首次申辦 LINE Pay 信用卡正卡，且可在核卡後30日內刷滿NT$888者。</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>新戶300點</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>新卡100點</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>活動期間 2026/7/1-2026/12/31 前申辦中國信託LINE Pay卡，且核准日須於 2027/1/15 前。核卡日起30日內以該新卡累積消費滿NT$888，可依資格領取新戶禮 LINE POINTS 300點，或新卡禮 LINE POINTS 100點。</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>點數回饋</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>新戶300點；新卡100點</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>新戶禮與新卡禮不可同時享有；每戶正卡限領乙次。</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>核卡日起30日內以該新卡累積消費滿NT$888。</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>新戶指申辦前12個月內未持有任何中國信託信用卡正卡；新卡指首次申辦LINE Pay信用卡正卡。須於刷卡前完成LINE Pay帳號綁定；點數將於符合資格之次次月起回饋至LINE Pay卡正卡綁定之LINE Pay帳號。</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/gifts.html</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>中信,LINE Pay,新戶禮,首刷禮,LINE POINTS,新卡禮</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>新戶禮／新卡禮</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>中國信託LINE Pay卡一卡通大眾交通1%回饋</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ctbc-linepay-ipass-transit-2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>transport</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026/1/1-12/31 使用已綁定的LINE Pay卡一卡通儲值金支付全臺大眾交通工具，高鐵與計程車除外，享LINE POINTS 1%。</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>以一卡通搭捷運、輕軌、台鐵、公車客運、公共自行車或渡輪，並已綁定LINE Pay卡者。</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>交通1%</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>回饋無上限</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>活動期間 2026/1/1-2026/12/31。持已綁定之中國信託LINE Pay信用卡或簽帳金融卡的一卡通功能，使用一卡通儲值金支付全臺大眾交通工具費用，可享 LINE POINTS 1%回饋。適用交通包含捷運輕軌、台鐵、公車客運、公共自行車、渡輪；高鐵與計程車除外。</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>點數回饋</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>回饋無上限；正附卡分開計算，信用卡與簽帳金融卡分開計算。每月：活動期間內當月份累積消費每滿NT$100，可獲得LINE POINT 1點。</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>須使用已綁定LINE Pay卡之一卡通功能支付全臺大眾交通工具，不含高鐵、計程車；也不包含以其他行動支付方之一卡通交易。消費明細依通路資料回傳時間為準。</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/index.html</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>中信,LINE Pay,一卡通,大眾交通,交通,捷運,台鐵,公車,LINE POINTS</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>一卡通大眾交通</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>聯邦綠卡指定生活代扣繳每月1%刷卡金</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ubot-green-card-utilities-autopay-2026h2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>cashback</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-07-01至12-31完成登錄，以聯邦綠卡綁水電瓦斯或電信費自動代扣繳並申辦電子化帳單，每月享1%刷卡金、上限NT$100</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>有固定水電、瓦斯或電信費帳單，想使用信用卡自動代扣繳並可申辦電子化帳單者。</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>完成活動登錄，並以聯邦綠卡綁定指定生活代扣繳與電子化帳單</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>指定生活代扣繳每月1%刷卡金</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-07-01至12-31，聯邦綠卡持卡人完成活動登錄後，綁定台灣自來水、台北自來水、台電、中華電信、台灣大哥大、遠傳電信、指定瓦斯公司或指定公有路邊停車費等生活代扣繳；申辦電子化帳單，即享每月1%刷卡金，月上限NT$100。</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>現金回饋</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>每月最高NT$100</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>活動期間完成登錄，以聯邦綠卡綁定指定生活代扣繳並申辦電子化帳單</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>生活代扣繳非一般消費，不提供原始卡片回饋；須以聯邦認定交易名稱為準。Visa金融卡、商務差旅卡、採購卡不適用；指定業者與完整條款以官方活動頁為準。</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://activity.ubot.com.tw/aws_act/2026/202607autopay/index.htm</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>水電瓦斯,電信費,加碼,需登錄,期間限定</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>官方活動頁查證；僅收錄聯邦綠卡專屬每月1%回饋，不將新申辦首扣贈刷卡金混列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>台新信用卡繳國內學雜費分期最優3.88%起</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>taishin-tuition-installment-2026h2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>installment</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-07-10至12-31，刷台新信用卡繳國內學雜費單筆滿NT$1,000，分3／6期利率3.88%起且0手續費</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>需繳國內學雜費並希望以信用卡分期付款的台新信用卡持卡人。</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>單筆學雜費滿NT$1,000</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>分3／6期3.88%、12期5.88%、18／24／30期8.88%，均0手續費</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-07-10至12-31，刷台新信用卡繳納幼稚園、國小、國高中、大專院校、進修推廣、國內美國學校及外僑學校等國內學雜費；單筆滿NT$1,000可享分3／6期3.88%、12期5.88%、18／24／30期8.88%優惠利率，均0手續費。</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>分期</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>3／6期3.88%起、0手續費</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>繳納前至官網登錄；數位通路免登錄。街口支付或悠遊付繳費後，須進線台新客服辦理分期</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>便利商店繳學雜費不適用。活動期間僅須登錄一次，後續每筆可享自動分期；如已設定指定卡片分期，欲參加本活動須進線台新客服。可繳學校與繳費帳號依繳款單及繳費平台公告為準。</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://mkpcard.taishinbank.com.tw/tscccms/promotion/detail/WM_20260617134739441</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>學費,分期,需登錄,期間限定</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>官方活動頁查證；全體適用台新信用卡，先連結既有台新Richart卡。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>台新街口聯名卡綁街口APP繳稅費最高2.15%</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>taishin-jkopay-card-bill-payments-2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>cashback</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026全年綁街口聯名卡於街口APP繳稅費，基本0.15%無上限；當月繳費滿NT$1,000再享2%街口券、每月上限20元</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>使用街口支付APP繳稅費或學雜費，且可每月累積NT$1,000繳費並手動領券的街口聯名卡持卡人。</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>當月街口APP繳費交易滿NT$1,000可取得加碼</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>基本0.15%街口幣無上限，加碼2%街口券</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-01-01至12-31，街口聯名卡綁定街口支付APP繳稅費可享基本0.15%回饋無上限；當月街口APP繳費交易滿NT$1,000，手動領券後可再享2%街口券，每月每人上限20元。官方頁另明載可用街口支付繳學雜費，實際可繳學校依街口支付公告為準。</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>最高2.15%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>加碼2%每月每人上限20元街口券；2026-07-01起每月限量55,000名</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>交易與回饋當下均在街口支付APP綁定街口聯名卡；達NT$1,000後至APP手動領取加碼券</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>領券以系統領取時間判定，額滿無法補領；加碼為街口券，可於全台7-ELEVEN折抵，非現金。若取消綁定本卡或註銷街口支付帳號，視同放棄回饋；繳納項目與學校依街口支付公告。</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://www.taishinbank.com.tw/TSB/personal/credit/intro/overview/future/24e1ad87-2cad-11f1-b50f-0050568c09e3</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>繳稅,學費,水電瓦斯,行動支付,加碼,需登錄,期間限定</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>官方活動頁與台新學雜費活動頁交叉查證；水／電等費用與學雜費均有台新官方頁明載。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>中國信託LINE Pay卡回饋計畫最高16%</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>cashback</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026下半年刷中國信託LINE Pay卡，國內外一般消費1%、國外實體信用卡最高2.8%，指定商家加碼最高16%。</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>想把日常、海外與指定商家消費累積為 LINE POINTS 的 LINE Pay 使用者。</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>國內外一般消費1%</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>指定商家加碼最高16%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>活動期間 2026/7/1-2026/12/31。使用中國信託LINE Pay卡或以 LINE Pay 綁定該卡支付，並於刷卡前完成 LINE Pay 帳號綁定，可累積 LINE POINTS。國內外一般消費享1%；信用卡於國外實體商店面對面交易最高2.8%；指定餐飲、網購、旅遊、生活等合作商家依各活動頁公告加碼，最高16%。</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>無上限；點數依消費金額四捨五入入點。</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>以中國信託LINE Pay卡結帳，或 LINE Pay 綁定中國信託LINE Pay卡支付。</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>需於刷卡消費前完成 LINE Pay 帳號綁定。分期交易不回饋 LINE POINTS；信用卡年費、利息、預借現金、基金、學費、稅款、公用事業費、政府規費、便利商店、全聯/大全聯、電信費、部分歐洲地區實體商店等官方列示項目不列入回饋。</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/index.html</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>中信,中國信託,LINE Pay,LINE POINTS,海外消費,一般消費,指定商家</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>補齊：正式站既有資料（多層回饋，3層），本次依 v7 多層寫法重新寫回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>國內外一般消費</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>最高2.8%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>無上限；含一般消費1%與國外實體商店加碼1.8%。</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>限信用卡於國外實體商店面對面交易，含實體卡與 Apple Pay／Google Pay／Samsung Pay。</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>網路交易、條碼支付、第三方支付不列入國外實體商店加碼；是否符合以中國信託及國際組織系統資料為準。需於刷卡消費前完成 LINE Pay 帳號綁定。分期交易不回饋 LINE POINTS；其餘不回饋項目同上。</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>國外實體商店</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-rewards-2026h2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>最高16%</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>各商家活動期間、登錄名額與回饋上限不同，依官網各活動頁為準。</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>需符合指定商家、指定卡別、指定消費日、滿額或登錄等條件。</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>部分商店位於百貨、商場、機場、車站、飯店或旅館時，可能因帳單明細不同而無法認列加碼。</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>指定商家加碼</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>中國信託LINE Pay卡海外實體消費周周登最高5%</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-overseas-physical-weekly-2026q3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026/7/1-9/30 持中國信託LINE Pay信用卡至國外實體商店消費，登錄後最高享 LINE POINTS 5%。</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026第三季有海外實體商店消費，且願意每週二搶登錄名額的 LINE Pay卡信用卡持卡人。</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>海外實體最高5%</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>每週二3,000名登錄名額</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>活動期間 2026/7/1-2026/9/30。持中國信託LINE Pay信用卡至國外實體商店消費，活動登錄後享 LINE POINTS 最高5%，包含國外實體一般消費2.8%與2.2%加碼回饋。每週二開放3,000名登錄名額。</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>最高5%</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>每週二開放3,000名登錄名額；實際仍以中國信託活動登錄頁公告為準。</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>須持中國信託LINE Pay信用卡於國外實體商店消費並完成活動登錄。</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>LINE Pay簽帳金融卡不適用此活動。國外實體交易認定與不回饋項目依中國信託官網與活動登錄頁公告為準。</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/index.html</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>中信,LINE Pay,海外,實體商店,周周登,LINE POINTS</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>海外實體周周登</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>中國信託LINE Pay卡新戶首刷禮最高300點</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-new-card-gift-2026h2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>cashback</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026/7/1-12/31 申辦 LINE Pay 卡，核卡日起30日內累積消費滿NT$888，新戶享300點、新卡享100點 LINE POINTS。</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>首次申辦中國信託信用卡或首次申辦 LINE Pay 信用卡正卡，且可在核卡後30日內刷滿NT$888者。</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>新戶300點</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>新卡100點</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>活動期間 2026/7/1-2026/12/31 前申辦中國信託LINE Pay卡，且核准日須於 2027/1/15 前。核卡日起30日內以該新卡累積消費滿NT$888，可依資格領取新戶禮 LINE POINTS 300點，或新卡禮 LINE POINTS 100點。</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>新戶300點；新卡100點</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>新戶禮與新卡禮不可同時享有；每戶正卡限領乙次。</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>核卡日起30日內以該新卡累積消費滿NT$888。</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>新戶指申辦前12個月內未持有任何中國信託信用卡正卡；新卡指首次申辦LINE Pay信用卡正卡。須於刷卡前完成LINE Pay帳號綁定；點數將於符合資格之次次月起回饋至LINE Pay卡正卡綁定之LINE Pay帳號。</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/gifts.html</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>中信,LINE Pay,新戶禮,首刷禮,LINE POINTS,新卡禮</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>新戶禮／新卡禮</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>中國信託LINE Pay卡一卡通大眾交通1%回饋</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ctbc-linepay-ipass-transit-2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026/1/1-12/31 使用已綁定的LINE Pay卡一卡通儲值金支付全臺大眾交通工具，高鐵與計程車除外，享LINE POINTS 1%。</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>以一卡通搭捷運、輕軌、台鐵、公車客運、公共自行車或渡輪，並已綁定LINE Pay卡者。</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>交通1%</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>回饋無上限</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>活動期間 2026/1/1-2026/12/31。持已綁定之中國信託LINE Pay信用卡或簽帳金融卡的一卡通功能，使用一卡通儲值金支付全臺大眾交通工具費用，可享 LINE POINTS 1%回饋。適用交通包含捷運輕軌、台鐵、公車客運、公共自行車、渡輪；高鐵與計程車除外。</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>點數回饋</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>回饋無上限；正附卡分開計算，信用卡與簽帳金融卡分開計算。每月：活動期間內當月份累積消費每滿NT$100，可獲得LINE POINT 1點。</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>須使用已綁定LINE Pay卡之一卡通功能支付全臺大眾交通工具，不含高鐵、計程車；也不包含以其他行動支付方之一卡通交易。消費明細依通路資料回傳時間為準。</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/index.html</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>中信,LINE Pay,一卡通,大眾交通,交通,捷運,台鐵,公車,LINE POINTS</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>一卡通大眾交通</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Richart卡7大方案最高3.8%</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>taishin-richart-category-rewards-2026h2</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>完成台新帳戶自扣後，Richart卡指定通路最高3.8%台新Point回饋。</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>日常消費通路多元、願意用Richart Life切換方案的使用者.</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>最高3.8%</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>7大方案</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>活動期間：2026/7/1-2027/3/31。
 持台新Richart卡並透過Richart Life APP切換指定方案，成功設定台新帳戶扣繳台新信用卡帳款後，於次期信用卡帳單結帳後次營業日起，指定通路最高享3.8%台新Point（信用卡）回饋；未完成設定者，切換刷加碼通路最高1.3%。一般消費另享0.3%回饋無上限。
 2026/7/8-9/30另有新上市7+1刷最高10%活動，實際通路、上限與領券規則依台新官網與Richart Life APP公告。</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>2027-03-31</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>點數回饋</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>指定通路最高3.8%；一般消費0.3%</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>各方案、領券與加碼活動依台新公告設定上限；一般消費0.3%無上限。</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>需透過Richart Life APP切換方案；成功設定台新帳戶自扣後才可升級指定通路最高3.8%。切換方案每日限一次，指定通路、支付方式、保費與不回饋交易依台新公告認定。</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>https://www.taishinbank.com.tw/TSB/personal/credit/intro/overview/cg047/?from=index</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>點數回饋,指定通路,行動支付,期間限定,保費</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>DAWHO新戶行動支付最高20%</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>dawho-mobile-payment-new-card-2026h2</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>新戶申辦DAWHO卡，核卡後30日內綁指定行動支付一般消費最高20%。</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>新辦永豐卡且常用LINE Pay、Apple Pay、Google Pay、Samsung Pay或全支付者。</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>新戶最高20%</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>上限500元</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>活動期間：2026/7/1-2026/12/31。
 新戶申辦DAWHO現金回饋信用卡，於核卡後30日內一般消費綁定LINE Pay、Apple Pay、Google Pay、Samsung Pay、全支付、55688 APP或Mitsui Shopping Park Pay支付，可享最高20%刷卡金回饋，回饋上限500元。
 本活動限2026/7/1-12/31申請進件，並於2027/1/15前核卡者參加，總限量10,000戶，額滿提前終止。</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>現金回饋</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>指定行動支付最高20%刷卡金</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>回饋上限500元；總限量10,000戶。</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>核卡後30日內指定行動支付一般消費</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>限新戶；指定行動支付交易須帳單明細有明確支付名稱，且最晚須於核卡60日內請款。一般消費定義、排除項目、回饋時間依永豐公告。</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>https://bank.sinopac.com/sinopacBT/personal/credit-card/introduction/bankcard/DAWHO.html?act=ACT211214009&amp;hpp=ACT211214009</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>現金回饋,新戶,行動支付,期間限定,需登錄</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>中信LINE Pay海外實體最高5%</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>ctbc-linepay-overseas-physical-2026q3</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>2026/7/1-9/30國外實體消費登錄後最高5% LINE POINTS。</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>暑期出國、海外實體刷卡或Apple Pay/Google Pay/Samsung Pay消費者。</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>海外最高5%</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>一般1%</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>活動期間：2026/7/1-2026/9/30。
 持中國信託LINE Pay信用卡至國外實體商店消費，登錄後享LINE POINTS最高5%，含國外一般消費2.8%與2.2%加碼回饋。國內外一般消費2026/7/1-12/31享1%，國外實體商店消費最高2.8%無上限。
 一卡通儲值金支付全臺大眾交通工具（高鐵除外）享LINE POINTS 1%。</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>點數回饋</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>海外實體最高5%；國外實體一般最高2.8%；國內外一般1%</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>海外實體5%加碼每週二開放3,000名登錄名額；一般與國外實體基本回饋依官方規則。</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>需登錄；國外實體商店須為面對面交易，網路交易、條碼支付或第三方支付不列入。分期交易無LINE POINTS回饋，本行不回饋項目依官方公告排除。</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/LINEPay/index.html</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>點數回饋,海外,旅遊交通,需登錄,期間限定,交通通勤</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>富邦momo卡店內最高3%</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>fubon-momo-shopping-2026h2</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>online-shopping</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>momo通路最高3%mo幣，店外一般與海外1%現金回饋無上限。</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>momo購物網、電視購物、mo店+與跨境電商重度使用者。</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>momo最高3%</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>新戶最高1,000</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>活動期間：2026/4/1-2026/12/31。
 持台北富邦momo卡於momo通路消費最高3% mo幣回饋；店外一般消費與海外消費享1%現金回饋無上限。momo通路包含購物網、電視購物、型錄、mo店+與跨境電商。
 2026/7/1-12/31新戶申辦momo卡正卡，核卡後30天內完成momo店內1筆與店外1筆一般消費，享700 mo幣與mo店+免運券；核卡後90天內店內與店外一般消費再享2%加碼，上限300 mo幣。</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>現金回饋</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>momo通路最高3% mo幣；店外與海外1%現金回饋；新戶加碼最高1,000 mo幣</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>momo通路每期帳單回饋上限1,000 mo幣；新戶加碼上限300 mo幣。</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>新戶首刷禮須核卡後30天內完成momo店內1筆與店外1筆一般消費。</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>新戶活動須於核卡後30天內登錄。特殊商品依商品頁標示，分期交易、回饋時間、帳號綁定與不適用項目依富邦公告。</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>https://www.fubon.com/banking/personal/credit_card/all_card/momo/momo.htm?fromUrl=web1206</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>現金回饋,網購電商,新戶,期間限定,指定通路</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>滙豐現金回饋國內1.22%</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>hsbc-cashback-signature-2026q3</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>現金回饋御璽卡國內1.22%、海外2.22%，無上限且回饋不歸零。</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>不想切換方案或登錄，想要低維護現金回饋者。</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>國內1.22%</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>海外2.22%</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>活動期間：2026/7/1-2026/9/30。
 滙豐現金回饋御璽卡新年度活動辦法公告維持不變，國內一般新增消費享現金積點1.22%，海外一般新增消費享2.22%。現金回饋無上限、無最低消費門檻，且回饋終身有效。</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>現金回饋</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>國內1.22%；海外2.22%</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>無上限。</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>海外2.22%不含歐盟及英國實體通路。合格消費、除外項目、活動辦法與後續延長期間依滙豐官方公告。</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>https://www.hsbc.com.tw/credit-cards/products/cashback-signature/</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>現金回饋,免切換,海外,長期權益</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>星展eco永續卡eco最高10%</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>dbs-eco-card-rewards-2026</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>一般消費1%無上限，指定海外實體最高5%、eco通路最高10%。</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>有海外實體、保費、超商街口支付、Tesla或Gogoro充電資費支出者。</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>一般1%無上限</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>eco最高10%</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>活動期間：2026/1/1-2026/12/31。
 星展eco永續卡國內／國外一般消費、保費與超商街口支付享1%現金積點回饋無上限。於日本、韓國、泰國、新加坡、美國、歐洲持卡或以Apple Pay／Samsung Pay於當地實體商店一般消費，享最高5%回饋；Tesla充電資費、Gogoro電池資費、星展支持的社會企業與中小企業等指定eco通路最高10%。
 2026/7/1-8/31新戶申辦另有首刷及指定任務好禮二選一。</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>現金回饋</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>一般消費1%；指定海外實體最高5%；指定eco通路最高10%</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>指定海外與eco通路加碼上限依星展官方權益規則。</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>最高5%與10%須符合指定國家、指定通路、支付方式與一般消費定義。回饋排除項目、現金積點規則與新戶首刷條件依星展公告。</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>https://www.dbs.com.tw/personal-zh/cards/landing/layout.html?pid=tw-pweb-personal-zh-cards-dbs_ipass-pxmart2</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>現金回饋,海外,保費,加油,交通通勤,期間限定</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>補齊：正式站既有資料，本次僅同步回 xlsx 存檔，未變更資料庫內容。</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>中國信託uniopen聯名卡消費回饋最高11%</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>ctbc-uniopen-core-rewards-2026h2</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>2026/7/1至8/31，國內一般消費1%，統一企業集團與海外消費依任務最高11% OPENPOINT。</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>統一企業集團品牌或海外實體消費比例高，並可完成uniopen會員連結與指定任務的持卡人。</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>國內一般消費1%無上限；統一企業集團基本加碼2%（每月上限500點）</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>不同統一企業集團品牌消費2至5家以上，踩點任務最高加碼4%（每月上限500點）</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>活動期間2026-07-01至2026-08-31。持中國信託uniopen聯名卡並於中信App連結uniopen會員：國內一般消費享1% OPENPOINT無上限；統一企業集團消費基本加碼2%，每月於不同品牌單筆消費滿NT$199，消費2家加碼1%、3家加碼2%、4家加碼3%、5家以上加碼4%；國外一般消費2%，國外實體商店依活動再加碼，整體最高可達11%。</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>點數回饋</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>最高11% OPENPOINT</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>統一企業集團基本加碼每戶每月500點；踩點任務每戶每月500點；海外實體加碼每戶每月500點。</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>統一企業集團踩點每個不同品牌單筆滿NT$199。</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>需核卡後登入中國信託銀行App連結uniopen會員；踩點須使用不同品牌；正附卡歸戶及回饋計算依銀行規則；不適用交易與實際認列通路依中國信託公告。卡優文章與icash Pay公告為交叉整理，官方規則優先。</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>https://www.ctbcbank.com/twrbo/zh_tw/cc_index/cc_product/cc_introduction_index/C_uniopen.html</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>點數回饋,指定通路,加碼,海外,期間限定,統一企業集團</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>交叉來源：https://www.cardu.com.tw/message/detail.php?63682；https://www.icashpay.com.tw/advertMessage/view/id/2370。</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>中國信託uniopen聯名卡綁定icash Pay單筆滿199加碼4%</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>ctbc-uniopen-icashpay-stack-2026q3</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>cashback</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>2026/7/1至8/31，綁定icash Pay於指定商店單筆滿NT$199，享4% OPENPOINT加碼。</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>平常使用icash Pay消費，且能完成綁卡與指定商店單筆門檻的uniopen持卡人。</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>icash Pay指定商店單筆滿NT$199加碼4%</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>可與uniopen統一企業集團踩點任務疊加，最高整理至7%或依品牌活動規則計算</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>活動期間2026-07-01至2026-08-31。以icash Pay綁定中國信託uniopen聯名卡，於指定商店單筆消費滿NT$199（含）享OPENPOINT加碼4%。每一icash Pay會員每月回饋上限150點，每月總回饋上限300萬點；可與uniopen聯名卡一般消費及統一企業集團踩點回饋疊加。icash Pay另有自動加值活動，需另行登錄，不能直接視為信用卡固有回饋。</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>點數回饋</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>加碼4% OPENPOINT</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>每一icash Pay會員每月150點；每月總回饋上限300萬點。</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>指定商店單筆滿NT$199。</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>需先將uniopen聯名卡綁定icash Pay；交易須符合指定商店與活動認列；icash Pay自動加值10%為另行登錄活動，適用卡版與活動條件依icash Pay公告。</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>https://www.icashpay.com.tw/advertMessage/view/id/2370</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>行動支付,點數回饋,加碼,指定通路,期間限定</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>交叉來源：https://www.ctbcbank.com/twrbo/zh_tw/cc_index/cc_product/cc_introduction_index/C_uniopen.html；https://www.cardu.com.tw/message/detail.php?63682。</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>中國信託uniopen聯名卡海外實體消費最高11%</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>ctbc-uniopen-overseas-physical-2026h2</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>2026/7/1至8/31，海外一般消費2%，海外實體商店再加碼，最高11% OPENPOINT。</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>有海外實體刷卡需求，並能接受每月加碼點數上限的uniopen持卡人。</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>海外一般消費2% OPENPOINT無上限</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>海外實體商店再加碼8%，整理後最高11%</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>活動期間2026-07-01至2026-08-31。持中國信託uniopen聯名卡於海外實體商店消費，享海外一般消費回饋，符合活動認列者再享海外實體商店加碼，整體最高11% OPENPOINT。海外實體加碼每戶每月上限500點；超過上限後仍依一般海外消費規則回饋。海外交易可能另有國外交易服務費，實際認列國家、商店型態、排除交易與回饋入點時間以中國信託公告為準。</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>點數回饋</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>最高11% OPENPOINT</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>海外實體商店加碼每戶每月500點；海外一般消費回饋無上限。</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>海外實體商店刷卡消費。</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>須完成uniopen會員連結；僅限銀行認列的海外實體商店交易；海外網路交易與不適用交易依官方規則辦理；實際回饋可能抵銷部分海外交易服務費但不代表免除費用。</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>https://www.ctbcbank.com/twrbo/zh_tw/cc_index/cc_product/cc_introduction_index/C_uniopen.html</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>海外,旅遊,點數回饋,加碼,期間限定</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>交叉來源：https://www.cardu.com.tw/message/detail.php?63682。</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>中國信託uniopen聯名卡統一企業集團指定品牌週期優惠</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>ctbc-uniopen-brand-weekly-promos-2026h2</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>dining</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2026/7/1至12/31，星巴克、foodomo、COLD STONE、博客來等統一企業集團品牌依指定日享優惠。</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>固定在統一企業集團指定品牌消費，願意依星期、門檻或App領券參加活動的持卡人。</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>星巴克每週一大杯飲料好友分享；COLD STONE指定日買1送1</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>foodomo週二滿NT$500贈50點；博客來週末滿NT$3,000最高加碼6%</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>活動期間依品牌公告，主要整理範圍為2026-07-01至2026-12-31。指定品牌與日期包含：星巴克週一購買兩杯大杯（含）以上飲料，其中一杯由星巴克招待；foodomo週二單筆滿NT$500贈OPENPOINT 50點，每月限量1,000名；COLD STONE週二及週五指定冰品買1送1；Yahoo購物中心／Yahoo拍賣週五累積滿NT$2,000且完成登錄享OPENPOINT 5%，每週上限200點、限量100名；博客來App週六日單筆滿NT$3,000最高加碼6%。夢時代與其他品牌優惠可能需於中國信託App領券，且各有名額、上限、指定商品或不可併用限制。</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>指定品牌買1送1／點數最高6%／滿額贈50點</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>各品牌依活動不同：foodomo每月限量1,000名；Yahoo每週上限200點且限量100名；博客來每戶每月上限200點；其他品牌依各自公告。</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>foodomo單筆滿NT$500；Yahoo累積滿NT$2,000；博客來單筆滿NT$3,000。</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>優惠依星期、品牌、支付方式及活動公告辦理；部分活動需於中信App領券或至平台登錄；名額額滿、商品售完、退貨或不適用支付方式均可能失去資格；不可與其他優惠合併者依品牌規則。</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>https://www.icashpay.com.tw/advertMessage/view/id/2370</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>指定通路,餐飲美食,點數回饋,需登錄,期間限定</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>官方交叉來源：https://www.ctbcbank.com/twrbo/zh_tw/cc_index/cc_product/cc_introduction_index/C_uniopen.html；https://www.cardu.com.tw/message/detail.php?63682；品牌細節以中信及各品牌最新公告為準。</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>中國信託華航聯名卡2026下半年哩程回饋</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>ctbc-china-airlines-mileage-rewards-2026h2</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>2026/7/1至12/31，三種卡等依消費類型累積華航哩程，生日月海外實體消費最高NT$6=1哩。</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>主要搭乘華航／華信航空，且可依卡等選擇哩程累積速度與年費的持卡人。</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>一般消費：鼎尊18元／哩、璀璨20元／哩、商務30元／哩</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>指定通路2倍；生日月海外實體3倍，鼎尊最優6元／哩</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>活動期間2026-07-01至2026-12-31。中國信託中華航空聯名卡依卡等累積華航哩程：鼎尊無限卡一般消費每NT$18=1哩、璀璨無限卡每NT$20=1哩、商務御璽卡每NT$30=1哩。國外實體商店、華航／華信航空官網機票、華航eMall、華航Sky Boutique、機上免稅品及指定訂房平台等享加碼2倍；生日當月國外實體商店享3倍，鼎尊無限卡最優NT$6=1哩。</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>點數回饋</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>最高NT$6=1哩</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>每月加碼哩程上限：鼎尊正卡80,000哩／附卡20,000哩；璀璨正卡60,000哩／附卡20,000哩；商務及各卡等附卡20,000哩。</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>依卡等與消費類型累積；生日月海外實體為生日當月消費。</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>須持有適用卡等；海外實體須為非台灣國別碼且面對面交易，Apple Pay、Google Pay、Samsung Pay於實體店可列入；網路交易、條碼支付、第三方支付及銀行不回饋交易不列入。指定訂房平台加碼限鼎尊／璀璨無限卡且須由帳單列示國外交易手續費。</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>旅遊,海外,點數回饋,加碼,期間限定,航空哩程</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>官方來源：https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html；卡優文章作為卡等比較與使用情境交叉整理。</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>中國信託華航聯名卡新戶迎賓與首刷哩程</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>ctbc-china-airlines-welcome-first-spend-2026h2</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>2026/7/1至12/31申請，依卡等完成綁定與首刷，最高可獲20,000哩。</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>首次申辦適用卡等，能在核卡後指定天數內完成一般消費並綁定華夏會員者。</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>鼎尊迎賓3,000哩＋核卡30天滿NT$8,888再贈17,000哩</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>璀璨迎賓2,000哩＋核卡30天滿NT$2,688再贈4,000哩；商務新戶滿NT$888贈1,000哩</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>申請收件日限2026-07-01至2026-12-31，且核准日須於2027-01-15前。鼎尊無限卡首次申辦綁定華夏會員並完成首刷享3,000哩，核卡30天內一般消費滿NT$8,888且繳交年費NT$22,000再享17,000哩；璀璨無限卡迎賓2,000哩，核卡30天內消費滿NT$2,688且繳年費NT$8,000再享4,000哩；商務御璽卡新戶核卡30天內消費滿NT$888享1,000哩。</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>點數回饋</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>最高20,000哩</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>迎賓禮限量30,000名；每戶正附卡合併限領一次；鼎尊／璀璨需繳交年費入帳。</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>鼎尊核卡30天一般消費滿NT$8,888；璀璨滿NT$2,688；商務滿NT$888。</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>新戶定義依卡等不同：鼎尊／璀璨為申辦前12個月未曾申辦任一中華航空聯名卡；商務為申辦前12個月未持有任何中信正卡（不含簽帳金融卡）。不含預借現金、基金申購、退貨、帳單分期、學費、繳稅、年費、手續費、利息及違約金等；首刷贈禮每戶限一次。</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>新戶,首刷,點數回饋,航空哩程,期間限定</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>官方來源：https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html；卡優文章補充三卡等迎賓與首刷比較。</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>中國信託華航聯名卡華夏金卡與機場尊榮禮遇</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>ctbc-china-airlines-elite-airport-benefits-2026h2</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>鼎尊／璀璨首次申辦綁定華夏會員並完成首刷，最優享華夏金卡會籍2年／1年及機場禮遇。</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>搭乘華航頻率高，重視優先報到、優先登機、貴賓室、機場接送與額外行李者。</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>鼎尊首次申辦綁定華夏會員且首刷，享金卡會籍2年</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>璀璨同條件享金卡會籍1年；鼎尊／璀璨另有華航貴賓室與機場接送次數</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>活動期間2026-07-01至2026-12-31。首次申辦鼎尊無限卡或璀璨無限卡，完成中華航空華夏會員綁定與首刷後，鼎尊最優享華夏金卡會籍2年、璀璨享1年。華夏金卡可享快速訂位、優先候補、機場專屬櫃檯、額外免費托運行李、優先裝卸行李及全球機場貴賓室等禮遇；鼎尊與璀璨並提供中華航空貴賓室及國際機場接送服務，次數依卡等公告。</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>華夏金卡會籍2年／1年；貴賓室與機場接送</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>鼎尊與璀璨的貴賓室、接送次數依卡等；每人金卡升等禮遇限一次。</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>完成華夏會員綁定與首刷；部分禮遇需於中信官網或行動銀行提出升等申請。</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>僅鼎尊與璀璨適用華夏金卡升等；商務御璽卡不適用。申請人原已為華夏金卡、翡翠卡或晶鑽卡者不再升等或延續效期；註銷卡片可能取消會籍。相關使用規範以中信與中華航空公告為準。</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>旅遊,航空哩程,機場貴賓室,機場接送,期間限定</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>官方來源：https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html；卡優文章補充三卡等機場禮遇比較。</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>中國信託華航聯名卡機票折扣與哩程兌換</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>ctbc-china-airlines-award-tickets-flight-discount-2026h2</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>travel</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>華航官網購票享依卡等機票優惠，華航酬賓機票9,000哩起可兌換香港單程經濟艙。</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>會搭乘華航／華信，願意累積OPENPOINT以外的華航哩程並使用酬賓機票者。</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>華航酬賓機票：台灣至香港經濟艙單程9,000哩起</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>華航官網國際航線機票依卡等最優86折起；哩程兌換涵蓋亞洲、澳洲、紐澳、北美與歐洲航線</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>活動期間2026-07-01至2026-12-31。持中國信託中華航空聯名卡於華航官網指定網頁購買國際航線機票，依卡等享機票優惠，卡優整理為最優86折起。華航酬賓機票可由9,000哩兌換台灣至香港經濟艙單程，香港來回18,000哩；亞洲線、紐澳、北美與歐洲依航線及艙等需要不同哩程。酬賓機票須綁定華夏會員並透過華航網站兌換，機位、稅費、燃油費與退改票規則另依華航公告。</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>折扣</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>機票86折起；9,000哩起兌換</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>酬賓機位依當時空位；退票手續費NT$1,500或等值當地貨幣；稅款與附加費由持票人負擔。</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>至少9,000哩兌換台灣至香港經濟艙單程；需綁定華夏會員並於起飛前依規定線上兌換。</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>機票折扣依卡等、航線、艙等與華航指定頁面而定；哩程不得兌換現金，效期與兌換規定依華航華夏酬賓計畫；未使用或改票、未登機可能產生費用。</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>旅遊,航空哩程,機票,折扣,期間限定</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>官方來源：https://www.ctbcbank.com/content/dam/minisite/long/creditcard/CTBCCI/index.html；卡優文章補充機票折扣與兌換門檻。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>星展PChome Prime聯名卡 PChome站內最高6%</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>dbs-pchome-prime-pchome-rewards-2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>online-shopping</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026年底前，PChome 24h購物與書店一般消費最高6%回饋。</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>常在PChome 24h購物或PChome 24h書店消費，願意綁定帳號並配合週四購物的使用者。</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>PChome站內最高6%</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>週四再加2% P幣</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026/1/1至2026/12/31，使用星展PChome Prime聯名卡於PChome 24h購物或PChome 24h書店一般消費，享2% PChome聯名點數；正卡綁定PChome帳號再享2% P幣；每週四以指定方式全額付款再加2% P幣，合計最高6%。PChome商店街與露天拍賣不適用。</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>等值點數</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2% PChome聯名點數</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>每期帳單週期上限1,000點</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>無最低消費</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>限PChome 24h購物與PChome 24h書店一般消費。PChome商店街、露天拍賣不適用；以交易入帳認定。</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>https://www.dbs.com.tw/personal-zh/cards/dbs-pchomeprime/index.html</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>指定通路,期間限定</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>同一優惠代號共三個回饋層級；P幣依v4模板規則列為等值點數。</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>PChome站內一般回饋</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>dbs-pchome-prime-pchome-rewards-2026</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>等值點數</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2% P幣</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>每期帳單週期上限1,000幣</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>正卡綁定PChome帳號</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>正卡須綁定PChome帳號；購買PChome儲值金或以儲值金付款不適用。</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>帳號綁定加碼</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>dbs-pchome-prime-pchome-rewards-2026</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>等值點數</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2% P幣</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>不計入一般P幣每期1,000幣上限</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>每週四以指定付款方式全額付款</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>限每週四以星展公告指定方式全額付款；購買PChome儲值金或以儲值金付款不適用。</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>週四加碼</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>星展PChome Prime聯名卡 指定海外電商最高3%</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>dbs-pchome-prime-selected-overseas-ecommerce-2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>online-shopping</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026年底前，指定海外電商外幣交易最高3%回饋。</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>會直接以本卡在指定海外電商進行外幣交易的使用者。</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>指定海外電商最高3%</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>活動期間P幣上限2,000幣</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026/1/1至2026/12/31，於星展公告指定海外電商以外幣交易，可享0.5% PChome聯名點數與2.5% P幣，合計最高3%。限直接刷卡的外幣交易，適用商店與排除項目依星展公告為準。</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>等值點數</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.5% PChome聯名點數</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>依星展公告</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>無最低消費</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>限星展公告的指定海外電商及外幣交易；行動支付、第三方支付等非直接刷卡交易不適用。</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>https://www.dbs.com.tw/personal-zh/cards/dbs-pchomeprime/index.html</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>海外,指定通路,期間限定</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>同一優惠代號共兩個回饋層級。</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>海外一般回饋</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>dbs-pchome-prime-selected-overseas-ecommerce-2026</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>等值點數</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2.5% P幣</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>活動期間總上限2,000幣</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>限指定海外電商外幣交易</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>指定海外電商、交易幣別與排除項目以星展公告為準。</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>指定海外電商加碼</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>國泰蝦皮購物聯名卡 蝦皮全站最高4%蝦幣</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>cathay-shopee-shopping-rewards-2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>online-shopping</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026年底前，蝦皮全站直接刷國泰蝦皮購物聯名卡，依月累積消費最高4%蝦幣。</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>每月蝦皮消費可累積至NT$3,000以上，且會直接使用聯名卡結帳的使用者。</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>滿NT$3,000最高4%</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>未滿NT$3,000最高3%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>至2026/12/31，直接使用國泰蝦皮購物聯名卡於蝦皮全站結帳，依每月帳單累積蝦皮全站消費金額，未滿NT$3,000最高3%蝦幣，滿NT$3,000最高4%蝦幣。最高回饋由蝦皮平台提供的回饋與國泰提供的蝦幣組成。</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>等值點數</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>最高3%蝦幣</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>國泰加碼年度上限20,000蝦幣點數／卡</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>當月帳單累積蝦皮全站消費未滿NT$3,000</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>限以本卡直接於蝦皮全站結帳。LINE Pay、街口支付、蝦皮廣告、海外消費（含蝦皮跨境）及其他非以本卡付款方式不適用。</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>https://www.cathaybk.com.tw/cathaybk/-/media/fddd4d9d98754438a663ee9129eb345a.pdf?sc_lang=en</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>指定通路,期間限定</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>同一優惠代號共兩個回饋層級；蝦幣依v4模板規則列為等值點數。</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>蝦皮全站未滿NT$3,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>cathay-shopee-shopping-rewards-2026</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>等值點數</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>最高4%蝦幣</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>國泰加碼年度上限20,000蝦幣點數／卡</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>當月帳單累積蝦皮全站消費滿NT$3,000</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>限以本卡直接於蝦皮全站結帳；其餘排除項目同本優惠第一層。</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>蝦皮全站滿NT$3,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>國泰蝦皮購物聯名卡 月月滿額免運券</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>cathay-shopee-shopping-free-shipping-2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>online-shopping</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>每月一般消費累積達指定金額或筆數，可獲1張蝦皮免運券。</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>每月一般消費可累積滿NT$5,000，或可完成5筆一般消費的蝦皮使用者。</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>滿NT$5,000或5筆消費</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>每月1張免運券</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>至2026/12/31，使用國泰蝦皮購物聯名卡，當月一般消費累積滿NT$5,000或一般消費滿5筆，可獲1張蝦皮免運券。免運券限以本卡於蝦皮購物結帳使用，並依蝦皮公告的適用配送方式、期限與門檻為準。</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>餐券贈品</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>每月1張蝦皮免運券</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>每月1張</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>當月一般消費累積滿NT$5,000或滿5筆</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>限以本卡於蝦皮購物結帳使用；適用配送方式、使用期限與其他限制依蝦皮公告。</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>https://www.cathaybk.com.tw/cathaybk/-/media/fddd4d9d98754438a663ee9129eb345a.pdf?sc_lang=en</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>指定通路,期間限定</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>免運券回饋</t>
         </is>
       </c>
     </row>
@@ -6314,7 +7448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.38000106811523" customWidth="1" min="1" max="1"/>
@@ -6951,6 +8085,54 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>dbs-pchome-prime-pchome-rewards-2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>dbs-pchome-prime-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>dbs-pchome-prime-selected-overseas-ecommerce-2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>dbs-pchome-prime-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cathay-shopee-shopping-rewards-2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>cathay-shopee-shopping-card</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cathay-shopee-shopping-free-shipping-2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>cathay-shopee-shopping-card</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
